--- a/VibeProject1/Assets/Table/Encounter/Encounter.xlsx
+++ b/VibeProject1/Assets/Table/Encounter/Encounter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Merchant\VibeProject1\Assets\Table\Encounter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD156586-E7E1-4699-9A3B-792DA102F576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41306D9-603E-4417-A2F4-DC6486B85C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28170" yWindow="1245" windowWidth="21405" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2910" windowWidth="21405" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Event" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -56,6 +56,51 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D1_Departure</t>
+  </si>
+  <si>
+    <t>Departure</t>
+  </si>
+  <si>
+    <t>Warrior01</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D2_AfterBattle</t>
+  </si>
+  <si>
+    <t>AfterBattle</t>
+  </si>
+  <si>
+    <t>Warrior01;Archer01</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D3_RandomQuestion</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>Archer01</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D4_SmallTalk</t>
+  </si>
+  <si>
+    <t>ManualRepeat</t>
   </si>
 </sst>
 </file>
@@ -434,7 +479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -458,6 +503,68 @@
       </c>
       <c r="G1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/VibeProject1/Assets/Table/Encounter/Encounter.xlsx
+++ b/VibeProject1/Assets/Table/Encounter/Encounter.xlsx
@@ -47,6 +47,54 @@
     <x:t>Conditions</x:t>
   </x:si>
   <x:si>
+    <x:t>E1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E1_BrokenCart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Random</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Once</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>E2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E2_Toll</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PerTrip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E3_Storm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E4_CartOwnerReturns</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fixed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Side</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flag:helped_cart</x:t>
+  </x:si>
+  <x:si>
     <x:t>Trigger</x:t>
   </x:si>
   <x:si>
@@ -83,9 +131,6 @@
     <x:t>D3_RandomQuestion</x:t>
   </x:si>
   <x:si>
-    <x:t>Random</x:t>
-  </x:si>
-  <x:si>
     <x:t>Archer01</x:t>
   </x:si>
   <x:si>
@@ -101,64 +146,37 @@
     <x:t>IllustrationKey</x:t>
   </x:si>
   <x:si>
+    <x:t>cart_owner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bandit_leader</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>E1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E1_BrokenCart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Once</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>E2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E2_Toll</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PerTrip</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E3_Storm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E4_CartOwnerReturns</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fixed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Side</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flag:helped_cart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cart_owner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bandit_leader</x:t>
-  </x:si>
-  <x:si>
     <x:t>수레 주인</x:t>
   </x:si>
   <x:si>
     <x:t>산적 두목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QE1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestTest_Event</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quest:Q_T1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QE2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestTest_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quest:Q_T3</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -536,94 +554,140 @@
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F7" s="0">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -655,10 +719,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F1" s="0" t="s">
         <x:v>5</x:v>
@@ -669,64 +733,64 @@
     </x:row>
     <x:row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -752,23 +816,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -794,12 +858,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>43</x:v>
@@ -807,7 +871,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>44</x:v>
